--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124418086</v>
+        <v>124416004</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380778</v>
+        <v>380983</v>
       </c>
       <c r="R3" t="n">
-        <v>6232125</v>
+        <v>6232111</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124416004</v>
+        <v>124418086</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>57532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380983</v>
+        <v>380778</v>
       </c>
       <c r="R4" t="n">
-        <v>6232111</v>
+        <v>6232125</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124415357</v>
+        <v>124418086</v>
       </c>
       <c r="B2" t="n">
-        <v>58218</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124416004</v>
+        <v>124415357</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>58218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380983</v>
+        <v>380778</v>
       </c>
       <c r="R3" t="n">
-        <v>6232111</v>
+        <v>6232125</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124418086</v>
+        <v>124416004</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380778</v>
+        <v>380983</v>
       </c>
       <c r="R4" t="n">
-        <v>6232125</v>
+        <v>6232111</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124418086</v>
+        <v>124415357</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>58218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124415357</v>
+        <v>124416004</v>
       </c>
       <c r="B3" t="n">
-        <v>58218</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380778</v>
+        <v>380983</v>
       </c>
       <c r="R3" t="n">
-        <v>6232125</v>
+        <v>6232111</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124416004</v>
+        <v>124418086</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>57532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380983</v>
+        <v>380778</v>
       </c>
       <c r="R4" t="n">
-        <v>6232111</v>
+        <v>6232125</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124416004</v>
+        <v>124418086</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380983</v>
+        <v>380778</v>
       </c>
       <c r="R3" t="n">
-        <v>6232111</v>
+        <v>6232125</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124418086</v>
+        <v>124416004</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380778</v>
+        <v>380983</v>
       </c>
       <c r="R4" t="n">
-        <v>6232125</v>
+        <v>6232111</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124415357</v>
+        <v>124418086</v>
       </c>
       <c r="B2" t="n">
-        <v>58218</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124418086</v>
+        <v>124415357</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>58218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124415357</v>
+        <v>124416004</v>
       </c>
       <c r="B3" t="n">
-        <v>58218</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380778</v>
+        <v>380983</v>
       </c>
       <c r="R3" t="n">
-        <v>6232125</v>
+        <v>6232111</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124416004</v>
+        <v>124415357</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>58218</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380983</v>
+        <v>380778</v>
       </c>
       <c r="R4" t="n">
-        <v>6232111</v>
+        <v>6232125</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124418086</v>
+        <v>124416004</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380778</v>
+        <v>380983</v>
       </c>
       <c r="R2" t="n">
-        <v>6232125</v>
+        <v>6232111</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124416004</v>
+        <v>124415357</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>58218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380983</v>
+        <v>380778</v>
       </c>
       <c r="R3" t="n">
-        <v>6232111</v>
+        <v>6232125</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124415357</v>
+        <v>124418086</v>
       </c>
       <c r="B4" t="n">
-        <v>58218</v>
+        <v>57532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,20 +927,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124416004</v>
+        <v>124418086</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380983</v>
+        <v>380778</v>
       </c>
       <c r="R2" t="n">
-        <v>6232111</v>
+        <v>6232125</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124418086</v>
+        <v>124416004</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380778</v>
+        <v>380983</v>
       </c>
       <c r="R4" t="n">
-        <v>6232125</v>
+        <v>6232111</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124415357</v>
+        <v>124416004</v>
       </c>
       <c r="B2" t="n">
-        <v>58218</v>
+        <v>57761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380778</v>
+        <v>380983</v>
       </c>
       <c r="R2" t="n">
-        <v>6232125</v>
+        <v>6232111</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124416004</v>
+        <v>124415357</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>58218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380983</v>
+        <v>380778</v>
       </c>
       <c r="R3" t="n">
-        <v>6232111</v>
+        <v>6232125</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>124418086</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,12 +793,7 @@
         <v>124416004</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,12 +908,7 @@
         <v>124415357</v>
       </c>
       <c r="B4" t="n">
-        <v>58218</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18559-2025 artfynd.xlsx
+++ b/artfynd/A 18559-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124418086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124416004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,8 +1032,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124415357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>